--- a/instrumentos/exemplos/DAIR_Checklist_Operacional_v0.3_EXEMPLO-INC-2026-001.xlsx
+++ b/instrumentos/exemplos/DAIR_Checklist_Operacional_v0.3_EXEMPLO-INC-2026-001.xlsx
@@ -362,13 +362,13 @@
     <t xml:space="preserve">CHK-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify &amp; Triage</t>
+    <t xml:space="preserve">Verify and Triage</t>
   </si>
   <si>
     <t xml:space="preserve">Confirmar a natureza do incidente</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais — mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica, ou alteração indevida de dados sem exfiltração)</t>
+    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais, qualquer que seja a causa — maliciosa, acidental ou ambiental (ex.: falha de infraestrutura, energia ou de provedor de nuvem) — mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica ou ambiental, ou alteração indevida de dados sem exfiltração)</t>
   </si>
   <si>
     <t xml:space="preserve">Logs e evidências preliminares disponíveis</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">Consulta indevida a 200 registros identificáveis confirmada (E02), com indicação de confidencialidade afetada</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) — confidencialidade, integridade, disponibilidade, autenticidade — foram afetadas</t>
+    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) — confidencialidade, integridade, disponibilidade, autenticidade — e qual causa (maliciosa, acidental ou ambiental) foram identificadas</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -2351,7 +2351,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>93</v>
       </c>
@@ -6389,7 +6389,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B24" type="list">
@@ -6417,7 +6417,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B25" type="list">
@@ -6445,7 +6445,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B26" type="list">
@@ -6473,7 +6473,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27" type="list">
@@ -6501,7 +6501,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B28" type="list">
@@ -6529,7 +6529,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B29" type="list">
@@ -6557,7 +6557,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B30" type="list">
@@ -6585,7 +6585,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B31" type="list">
@@ -6613,7 +6613,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B32" type="list">
@@ -6641,7 +6641,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B33" type="list">
@@ -6669,7 +6669,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B34" type="list">
@@ -6697,7 +6697,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B35" type="list">
@@ -6725,7 +6725,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B36" type="list">
@@ -6753,7 +6753,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B37" type="list">
@@ -6781,7 +6781,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C38" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B38" type="list">
@@ -6809,7 +6809,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C39" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B39" type="list">
@@ -6837,7 +6837,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C40" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B40" type="list">
@@ -6865,7 +6865,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B41" type="list">
@@ -6893,7 +6893,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C42" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B42" type="list">
@@ -6921,7 +6921,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C43" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B43" type="list">
@@ -6949,7 +6949,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C44" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B44" type="list">
@@ -6977,7 +6977,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C45" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B45" type="list">
@@ -7005,7 +7005,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C46" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B46" type="list">
@@ -7033,7 +7033,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C47" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B47" type="list">
@@ -7061,7 +7061,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C48" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B48" type="list">
@@ -7089,7 +7089,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C49" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B49" type="list">
@@ -7117,7 +7117,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C50" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B50" type="list">
@@ -7145,7 +7145,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C51" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B51" type="list">
@@ -7173,7 +7173,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C52" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B52" type="list">
@@ -7201,7 +7201,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C53" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B53" type="list">
@@ -7229,7 +7229,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C54" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B54" type="list">
@@ -7257,7 +7257,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C55" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B55" type="list">
@@ -7285,7 +7285,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C56" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B56" type="list">
@@ -7313,7 +7313,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C57" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B57" type="list">
@@ -7341,7 +7341,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C58" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B58" type="list">
@@ -7369,7 +7369,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C59" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B59" type="list">
@@ -7397,7 +7397,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B60" type="list">
@@ -7425,7 +7425,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C61" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B61" type="list">
@@ -7453,7 +7453,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C62" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B62" type="list">
@@ -7481,7 +7481,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C63" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B63" type="list">
@@ -7509,7 +7509,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C64" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B64" type="list">
@@ -7537,7 +7537,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C65" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B65" type="list">
@@ -7565,7 +7565,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C66" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B66" type="list">
@@ -7593,7 +7593,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C67" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B67" type="list">
@@ -7621,7 +7621,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C68" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B68" type="list">
@@ -7649,7 +7649,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C69" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B69" type="list">
@@ -7677,7 +7677,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C70" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B70" type="list">
@@ -7705,7 +7705,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C71" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B71" type="list">
@@ -7733,7 +7733,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C72" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B72" type="list">
@@ -7761,7 +7761,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C73" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B73" type="list">
@@ -7789,7 +7789,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C74" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B74" type="list">
@@ -7817,7 +7817,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C75" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B75" type="list">
@@ -7845,7 +7845,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C76" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B76" type="list">
@@ -7873,7 +7873,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C77" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B77" type="list">
@@ -7901,7 +7901,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C78" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B78" type="list">
@@ -7929,7 +7929,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C79" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B79" type="list">
@@ -7957,7 +7957,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C80" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B80" type="list">
@@ -7985,7 +7985,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C81" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B81" type="list">
@@ -8013,7 +8013,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C82" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B82" type="list">
@@ -8041,7 +8041,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C83" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B83" type="list">
@@ -8069,7 +8069,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C84" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B84" type="list">
@@ -8097,7 +8097,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C85" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B85" type="list">
@@ -8125,7 +8125,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C86" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B86" type="list">
@@ -8153,7 +8153,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C87" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B87" type="list">
@@ -8181,7 +8181,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C88" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B88" type="list">
@@ -8209,7 +8209,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C89" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B89" type="list">
@@ -8237,7 +8237,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C90" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B90" type="list">
@@ -8265,7 +8265,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C91" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B91" type="list">
@@ -8293,7 +8293,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C92" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B92" type="list">
@@ -8321,7 +8321,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C93" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B93" type="list">
@@ -8349,7 +8349,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C94" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B94" type="list">
@@ -8377,7 +8377,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C95" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B95" type="list">
@@ -8405,7 +8405,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C96" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B96" type="list">
@@ -8433,7 +8433,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C97" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B97" type="list">
@@ -8461,7 +8461,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C98" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B98" type="list">
@@ -8489,7 +8489,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C99" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B99" type="list">
@@ -8517,7 +8517,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C100" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B100" type="list">
@@ -8545,7 +8545,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C101" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B101" type="list">
@@ -8573,7 +8573,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C102" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B102" type="list">
@@ -8601,7 +8601,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C103" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B103" type="list">
@@ -8629,7 +8629,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C104" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B104" type="list">
@@ -8657,7 +8657,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C105" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B105" type="list">
@@ -8685,7 +8685,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C106" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B106" type="list">
@@ -8713,7 +8713,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C107" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B107" type="list">
@@ -8741,7 +8741,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C108" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B108" type="list">
@@ -8769,7 +8769,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C109" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B109" type="list">
@@ -8797,7 +8797,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C110" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B110" type="list">
@@ -8825,7 +8825,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C111" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B111" type="list">
@@ -8853,7 +8853,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C112" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B112" type="list">
@@ -8881,7 +8881,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C113" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B113" type="list">
@@ -8909,7 +8909,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C114" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B114" type="list">
@@ -8937,7 +8937,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C115" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B115" type="list">
@@ -8965,7 +8965,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C116" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B116" type="list">
@@ -8993,7 +8993,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C117" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B117" type="list">
@@ -9021,7 +9021,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C118" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B118" type="list">
@@ -9049,7 +9049,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C119" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B119" type="list">
@@ -9077,7 +9077,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C120" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B120" type="list">
@@ -9105,7 +9105,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C121" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B121" type="list">
@@ -9133,7 +9133,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C122" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B122" type="list">
@@ -9161,7 +9161,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C123" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B123" type="list">
@@ -9189,7 +9189,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C124" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B124" type="list">
@@ -9217,7 +9217,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C125" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B125" type="list">
@@ -9245,7 +9245,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C126" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B126" type="list">
@@ -9273,7 +9273,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C127" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B127" type="list">
@@ -9301,7 +9301,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C128" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B128" type="list">
@@ -9329,7 +9329,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C129" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B129" type="list">
@@ -9357,7 +9357,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C130" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B130" type="list">
@@ -9385,7 +9385,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C131" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B131" type="list">
@@ -9413,7 +9413,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C132" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B132" type="list">
@@ -9441,7 +9441,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C133" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B133" type="list">
@@ -9469,7 +9469,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C134" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B134" type="list">
@@ -9497,7 +9497,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C135" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B135" type="list">
@@ -9525,7 +9525,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C136" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B136" type="list">
@@ -9553,7 +9553,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C137" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B137" type="list">
@@ -9581,7 +9581,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C138" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B138" type="list">
@@ -9609,7 +9609,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C139" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B139" type="list">
@@ -9637,7 +9637,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C140" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B140" type="list">
@@ -9665,7 +9665,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C141" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B141" type="list">
@@ -9693,7 +9693,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C142" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B142" type="list">
@@ -9721,7 +9721,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C143" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B143" type="list">
@@ -9749,7 +9749,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C144" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B144" type="list">
@@ -9777,7 +9777,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C145" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B145" type="list">
@@ -9805,7 +9805,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C146" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B146" type="list">
@@ -9833,7 +9833,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C147" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B147" type="list">
@@ -9861,7 +9861,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C148" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B148" type="list">
@@ -9889,7 +9889,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C149" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B149" type="list">
@@ -9917,7 +9917,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C150" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B150" type="list">
@@ -9945,7 +9945,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C151" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B151" type="list">
@@ -9973,7 +9973,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C152" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B152" type="list">
@@ -10001,7 +10001,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C153" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B153" type="list">
